--- a/artfynd/A 12024-2022 artfynd.xlsx
+++ b/artfynd/A 12024-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128900456</v>
       </c>
       <c r="B2" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128900468</v>
       </c>
       <c r="B3" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>128900460</v>
       </c>
       <c r="B4" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
         <v>128900466</v>
       </c>
       <c r="B5" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>128900458</v>
       </c>
       <c r="B6" t="n">
-        <v>75205</v>
+        <v>75209</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>128900464</v>
       </c>
       <c r="B7" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>128900462</v>
       </c>
       <c r="B8" t="n">
-        <v>91958</v>
+        <v>91962</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 12024-2022 artfynd.xlsx
+++ b/artfynd/A 12024-2022 artfynd.xlsx
@@ -979,10 +979,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128900466</v>
+        <v>128900458</v>
       </c>
       <c r="B5" t="n">
-        <v>79124</v>
+        <v>75209</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -990,21 +990,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1014,10 +1014,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594302</v>
+        <v>594385</v>
       </c>
       <c r="R5" t="n">
-        <v>6981569</v>
+        <v>6981554</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,10 +1076,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128900458</v>
+        <v>128900466</v>
       </c>
       <c r="B6" t="n">
-        <v>75209</v>
+        <v>79124</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1087,21 +1087,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594385</v>
+        <v>594302</v>
       </c>
       <c r="R6" t="n">
-        <v>6981554</v>
+        <v>6981569</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 12024-2022 artfynd.xlsx
+++ b/artfynd/A 12024-2022 artfynd.xlsx
@@ -979,10 +979,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128900458</v>
+        <v>128900466</v>
       </c>
       <c r="B5" t="n">
-        <v>75209</v>
+        <v>79124</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -990,21 +990,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1014,10 +1014,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594385</v>
+        <v>594302</v>
       </c>
       <c r="R5" t="n">
-        <v>6981554</v>
+        <v>6981569</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,10 +1076,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128900466</v>
+        <v>128900458</v>
       </c>
       <c r="B6" t="n">
-        <v>79124</v>
+        <v>75209</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1087,21 +1087,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594302</v>
+        <v>594385</v>
       </c>
       <c r="R6" t="n">
-        <v>6981569</v>
+        <v>6981554</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 12024-2022 artfynd.xlsx
+++ b/artfynd/A 12024-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128900456</v>
       </c>
       <c r="B2" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128900468</v>
       </c>
       <c r="B3" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>128900460</v>
       </c>
       <c r="B4" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
         <v>128900466</v>
       </c>
       <c r="B5" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>128900458</v>
       </c>
       <c r="B6" t="n">
-        <v>75209</v>
+        <v>83005</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>128900464</v>
       </c>
       <c r="B7" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>128900462</v>
       </c>
       <c r="B8" t="n">
-        <v>91962</v>
+        <v>91967</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 12024-2022 artfynd.xlsx
+++ b/artfynd/A 12024-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128900456</v>
       </c>
       <c r="B2" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>128900464</v>
       </c>
       <c r="B7" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>128900462</v>
       </c>
       <c r="B8" t="n">
-        <v>91975</v>
+        <v>91978</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 12024-2022 artfynd.xlsx
+++ b/artfynd/A 12024-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128900456</v>
       </c>
       <c r="B2" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128900468</v>
       </c>
       <c r="B3" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
         <v>128900466</v>
       </c>
       <c r="B5" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>128900458</v>
       </c>
       <c r="B6" t="n">
-        <v>83010</v>
+        <v>83011</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>128900464</v>
       </c>
       <c r="B7" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>128900462</v>
       </c>
       <c r="B8" t="n">
-        <v>91978</v>
+        <v>91981</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 12024-2022 artfynd.xlsx
+++ b/artfynd/A 12024-2022 artfynd.xlsx
@@ -979,10 +979,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128900466</v>
+        <v>128900458</v>
       </c>
       <c r="B5" t="n">
-        <v>79035</v>
+        <v>83011</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -990,21 +990,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1014,10 +1014,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594302</v>
+        <v>594385</v>
       </c>
       <c r="R5" t="n">
-        <v>6981569</v>
+        <v>6981554</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,10 +1076,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128900458</v>
+        <v>128900466</v>
       </c>
       <c r="B6" t="n">
-        <v>83011</v>
+        <v>79035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1087,21 +1087,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594385</v>
+        <v>594302</v>
       </c>
       <c r="R6" t="n">
-        <v>6981554</v>
+        <v>6981569</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 12024-2022 artfynd.xlsx
+++ b/artfynd/A 12024-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128900456</v>
       </c>
       <c r="B2" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128900468</v>
       </c>
       <c r="B3" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>128900460</v>
       </c>
       <c r="B4" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,10 +979,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128900458</v>
+        <v>128900466</v>
       </c>
       <c r="B5" t="n">
-        <v>83011</v>
+        <v>79039</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -990,21 +990,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1014,10 +1014,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594385</v>
+        <v>594302</v>
       </c>
       <c r="R5" t="n">
-        <v>6981554</v>
+        <v>6981569</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,10 +1076,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128900466</v>
+        <v>128900458</v>
       </c>
       <c r="B6" t="n">
-        <v>79035</v>
+        <v>83015</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1087,21 +1087,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594302</v>
+        <v>594385</v>
       </c>
       <c r="R6" t="n">
-        <v>6981569</v>
+        <v>6981554</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1176,7 +1176,7 @@
         <v>128900464</v>
       </c>
       <c r="B7" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>128900462</v>
       </c>
       <c r="B8" t="n">
-        <v>91981</v>
+        <v>91988</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 12024-2022 artfynd.xlsx
+++ b/artfynd/A 12024-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128900456</v>
       </c>
       <c r="B2" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>128900458</v>
       </c>
       <c r="B6" t="n">
-        <v>83015</v>
+        <v>83005</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>128900464</v>
       </c>
       <c r="B7" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>128900462</v>
       </c>
       <c r="B8" t="n">
-        <v>91988</v>
+        <v>91995</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 12024-2022 artfynd.xlsx
+++ b/artfynd/A 12024-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128900456</v>
       </c>
       <c r="B2" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128900468</v>
       </c>
       <c r="B3" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>128900460</v>
       </c>
       <c r="B4" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
         <v>128900466</v>
       </c>
       <c r="B5" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>128900458</v>
       </c>
       <c r="B6" t="n">
-        <v>83005</v>
+        <v>83007</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>128900464</v>
       </c>
       <c r="B7" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>128900462</v>
       </c>
       <c r="B8" t="n">
-        <v>91995</v>
+        <v>91997</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 12024-2022 artfynd.xlsx
+++ b/artfynd/A 12024-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128900456</v>
       </c>
       <c r="B2" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>128900464</v>
       </c>
       <c r="B7" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>128900462</v>
       </c>
       <c r="B8" t="n">
-        <v>91997</v>
+        <v>91992</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1290,12 +1290,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>

--- a/artfynd/A 12024-2022 artfynd.xlsx
+++ b/artfynd/A 12024-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128900456</v>
       </c>
       <c r="B2" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>128900464</v>
       </c>
       <c r="B7" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>128900462</v>
       </c>
       <c r="B8" t="n">
-        <v>91992</v>
+        <v>91993</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 12024-2022 artfynd.xlsx
+++ b/artfynd/A 12024-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128900456</v>
       </c>
       <c r="B2" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128900468</v>
       </c>
       <c r="B3" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -979,10 +979,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128900466</v>
+        <v>128900458</v>
       </c>
       <c r="B5" t="n">
-        <v>79041</v>
+        <v>83011</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -990,21 +990,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1014,10 +1014,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594302</v>
+        <v>594385</v>
       </c>
       <c r="R5" t="n">
-        <v>6981569</v>
+        <v>6981554</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,10 +1076,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128900458</v>
+        <v>128900466</v>
       </c>
       <c r="B6" t="n">
-        <v>83007</v>
+        <v>79043</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1087,21 +1087,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594385</v>
+        <v>594302</v>
       </c>
       <c r="R6" t="n">
-        <v>6981554</v>
+        <v>6981569</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1176,7 +1176,7 @@
         <v>128900464</v>
       </c>
       <c r="B7" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>128900462</v>
       </c>
       <c r="B8" t="n">
-        <v>91993</v>
+        <v>91996</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 12024-2022 artfynd.xlsx
+++ b/artfynd/A 12024-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128900456</v>
       </c>
       <c r="B2" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128900468</v>
       </c>
       <c r="B3" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -979,10 +979,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128900458</v>
+        <v>128900466</v>
       </c>
       <c r="B5" t="n">
-        <v>83011</v>
+        <v>79044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -990,21 +990,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1014,10 +1014,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594385</v>
+        <v>594302</v>
       </c>
       <c r="R5" t="n">
-        <v>6981554</v>
+        <v>6981569</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,10 +1076,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128900466</v>
+        <v>128900458</v>
       </c>
       <c r="B6" t="n">
-        <v>79043</v>
+        <v>83012</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1087,21 +1087,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594302</v>
+        <v>594385</v>
       </c>
       <c r="R6" t="n">
-        <v>6981569</v>
+        <v>6981554</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1176,7 +1176,7 @@
         <v>128900464</v>
       </c>
       <c r="B7" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>128900462</v>
       </c>
       <c r="B8" t="n">
-        <v>91996</v>
+        <v>91998</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 12024-2022 artfynd.xlsx
+++ b/artfynd/A 12024-2022 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128900456</v>
+        <v>128900462</v>
       </c>
       <c r="B2" t="n">
-        <v>92827</v>
+        <v>92369</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>1209</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>594368</v>
+        <v>594401</v>
       </c>
       <c r="R2" t="n">
-        <v>6981524</v>
+        <v>6981572</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128900468</v>
+        <v>128900456</v>
       </c>
       <c r="B3" t="n">
-        <v>79044</v>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,37 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gussjöudden, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594348</v>
+        <v>594368</v>
       </c>
       <c r="R3" t="n">
-        <v>6981488</v>
+        <v>6981524</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -854,7 +851,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -873,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128900460</v>
+        <v>128900464</v>
       </c>
       <c r="B4" t="n">
-        <v>57727</v>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -884,38 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gussjöudden, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594419</v>
+        <v>594302</v>
       </c>
       <c r="R4" t="n">
-        <v>6981550</v>
+        <v>6981575</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -948,11 +940,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-05</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -982,11 +969,11 @@
         <v>128900466</v>
       </c>
       <c r="B5" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1076,45 +1063,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128900458</v>
+        <v>128900468</v>
       </c>
       <c r="B6" t="n">
-        <v>83012</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gussjöudden, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594385</v>
+        <v>594348</v>
       </c>
       <c r="R6" t="n">
-        <v>6981554</v>
+        <v>6981488</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1155,6 +1145,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1173,32 +1164,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128900464</v>
+        <v>128900458</v>
       </c>
       <c r="B7" t="n">
-        <v>92827</v>
+        <v>83307</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1208,10 +1199,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594302</v>
+        <v>594385</v>
       </c>
       <c r="R7" t="n">
-        <v>6981575</v>
+        <v>6981554</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1270,45 +1261,49 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128900462</v>
+        <v>128900460</v>
       </c>
       <c r="B8" t="n">
-        <v>91998</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gussjöudden, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594401</v>
+        <v>594419</v>
       </c>
       <c r="R8" t="n">
-        <v>6981572</v>
+        <v>6981550</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1341,6 +1336,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 12024-2022 artfynd.xlsx
+++ b/artfynd/A 12024-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128900462</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128900456</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128900464</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128900466</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1161,6 +1186,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128900468</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1258,6 +1288,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128900458</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1364,8 +1399,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128900460</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>